--- a/plantillas_excel/31_exportar_notas.xlsx
+++ b/plantillas_excel/31_exportar_notas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="EXPORTAR_NOTAS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EXPORTAR_NOTAS_RESULTADOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -608,80 +609,63 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Service_Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo_Nota</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>DETALLE_PROCESO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Texto_Exportado</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>IGR</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>1RIOTU</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>PARBR1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>EX</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>UES</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>EJEMPLO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -694,7 +678,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Service_Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Codigo_Nota</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>DETALLE_PROCESO</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Texto_Exportado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Hoja de salida — la completa el script. No hace falta escribir nada acá.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -705,414 +750,386 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Exportar Notas (50)</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Exportar Notas (31)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Exporta a una columna del Excel el contenido de una nota (Product Notes) ya existente en un producto. El código de nota no está limitado a una lista fija.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exporta notas (Product Notes) de una lista de product codes. Qué notas exportar se elige en la pestaña de la app (no en el Excel) — los resultados se agregan a la hoja EXPORTAR_NOTAS_RESULTADOS, una fila por producto × nota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Hoja de datos a completar: "EXPORTAR_NOTAS"</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Columnas del Excel</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Columna</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Obligatoria</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Formato / Valores</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Qué significa</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Ejemplo</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Texto (código de Location de Tourplan)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Ubicación del producto madre a buscar.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>IGR</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Texto (código de Supplier)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Proveedor del producto madre.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1RIOTU</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Texto (código del producto)</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Código del producto/servicio madre.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>PARBR1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Service_Type</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sigla de 2 letras (HT, HX, TF, EX, ML, RT, CR, FT, OC, LN, LP, MS)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Tipo de servicio, usado para filtrar/desambiguar en Product Search.</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>EX</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Codigo_Nota</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Texto libre (código de la nota tal como figura en Tourplan)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Código de la nota puntual a buscar dentro de Product Notes del producto. A diferencia de Notas SRV, no está limitado a una lista fija.</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>UES</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PENDIENTE / EXPORTADO / PARCIAL / ERROR...</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Controla qué filas procesa el script.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EJEMPLO</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>ESTADO</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>PENDIENTE / EXPORTADA / NO EXISTE / ERROR...</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Controla qué filas procesa el script.</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>EJEMPLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>DETALLE_PROCESO</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Texto (la escribe el script)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Detalle del resultado (por ejemplo fecha de creación/actualización y autor). Podés dejarla vacía.</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr"/>
-    </row>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Resumen de cuántas notas se exportaron bien sobre el total configurado (ver "Valores posibles de ESTADO" abajo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1"/>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Texto_Exportado</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Texto (la escribe el script)</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Contenido de la nota, convertido de HTML a texto plano. Se llena solo si ESTADO queda en EXPORTADA.</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Qué notas exportar — se elige en la app, no en el Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>En la pestaña "Exportar" de la app, Paso 1 es un buscador donde elegís una o varias de: Nota SRV, Descriptivo, Título, Luggage Waiver (las 4 con variante de idioma), o directamente Dirección Rent a Car, Producto Coordinates, Remodelación Hotel, Nota Cliente Solo Voucher, External Option - Mapeo Específico (sin variante de idioma, van directo). Para cada una de las 4 familias con idioma, Paso 2 muestra checkboxes (Alemán/Español/Francés/Inglés/Italiano) para tildar cuáles necesitás — por default vienen todos tildados.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Valores posibles de ESTADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Esa selección aplica igual para TODAS las filas PENDIENTE de la corrida — no es un valor por fila del Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hoja de salida: "EXPORTAR_NOTAS_RESULTADOS"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>El script agrega ahí una fila por cada producto × nota exportada — nunca actualiza una fila existente, siempre suma filas nuevas (incluso si volvés a correr sobre el mismo producto en otra corrida). Columnas: Location, Supplier, Service_Type, Code, Codigo_Nota, ESTADO (EXPORTADA / NO EXISTE / ERROR: ...), DETALLE_PROCESO (fecha de creación/actualización y autor), Texto_Exportado (contenido de la nota, de HTML a texto plano).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Esta pestaña tiene que existir de antemano en el Sheet (ya viene en esta plantilla) — si la borrás, el script no la crea solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Valores posibles de ESTADO (en EXPORTAR_NOTAS, por producto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Significado</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Fila a procesar (es de solo lectura, así que siempre "ejecuta" — no tiene modo lectura/aplicar).</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>EXPORTADA</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>La nota existe y se exportó su texto a Texto_Exportado.</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="13" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>NO EXISTE</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>El producto se encontró pero ningún código de Product Notes coincide con Codigo_Nota.</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>ERROR: producto no encontrado — ...</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Product Search no devolvió el producto.</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>ERROR: &lt;otros detalles&gt;</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Otros fallos técnicos (no cargó la tabla de notas, no se pudo leer el contenido, etc.).</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="13" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EXPORTADO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Se exportaron bien TODAS las notas configuradas para ese producto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Al menos una nota se exportó bien y al menos una falló (no existe, error técnico, etc.) — ver el detalle de cada una en EXPORTAR_NOTAS_RESULTADOS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ninguna nota se pudo exportar — incluye el caso de no encontrar/abrir el producto en Tourplan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Reglas para completar el Excel</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>•  Si falta cualquiera de Location/Supplier/Code/Service_Type/Codigo_Nota, la fila queda en ERROR ("faltan campos obligatorios") sin tocar Tourplan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>•  Si varias filas comparten el mismo producto (Location+Supplier+Code+Service_Type) con distinto Codigo_Nota, conviene ponerlas seguidas: el script agrupa y reutiliza la búsqueda/apertura del producto para todas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>•  Si falta cualquiera de Location/Supplier/Code/Service_Type, la fila queda en ERROR ("faltan campos obligatorios") sin tocar Tourplan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>•  Una fila = un product code. No hace falta repetir filas por cada nota — el script exporta todas las notas configuradas (Paso 1/Paso 2 de la app) sobre cada producto, en una sola pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>•  Es un script de solo lectura: nunca inserta, edita ni guarda nada en Tourplan.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>La fila 2 de la hoja de datos es un EJEMPLO (no se procesa: ESTADO=EJEMPLO). Borrala o reemplazala por tus propias filas, y poné ESTADO=PENDIENTE en cada una para que el script la procese.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
